--- a/04_Figures/F04_association/modules/T3/limma/c_data/results.xlsx
+++ b/04_Figures/F04_association/modules/T3/limma/c_data/results.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <si>
     <t xml:space="preserve">outcome</t>
   </si>
@@ -70,12 +70,6 @@
   </si>
   <si>
     <t xml:space="preserve">ME_red</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_salmon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_tan</t>
   </si>
   <si>
     <t xml:space="preserve">ME_turquoise</t>
@@ -492,16 +486,16 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>0.000165730286504689</v>
+        <v>-0.0075918871133088</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0370464645893646</v>
+        <v>-1.70772003381248</v>
       </c>
       <c r="F2" t="n">
-        <v>0.970491681144286</v>
+        <v>0.0898583549406633</v>
       </c>
       <c r="G2" t="n">
-        <v>0.970491681144286</v>
+        <v>0.197688380869459</v>
       </c>
     </row>
     <row r="3">
@@ -515,16 +509,16 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.0105821896497919</v>
+        <v>0.0015673586084665</v>
       </c>
       <c r="E3" t="n">
-        <v>-2.36548625122822</v>
+        <v>0.352561840804313</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0191401054932542</v>
+        <v>0.72493604550352</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0622053428530762</v>
+        <v>0.886032944504302</v>
       </c>
     </row>
     <row r="4">
@@ -538,16 +532,16 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.0110840145700738</v>
+        <v>-0.00999515830130921</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.47766151823206</v>
+        <v>-2.24831215447744</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0142074596787827</v>
+        <v>0.0260857309617124</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0622053428530762</v>
+        <v>0.0956476801929456</v>
       </c>
     </row>
     <row r="5">
@@ -561,16 +555,16 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>0.000502712031512815</v>
+        <v>0.00800151364468614</v>
       </c>
       <c r="E5" t="n">
-        <v>0.112373567118405</v>
+        <v>1.7998614768521</v>
       </c>
       <c r="F5" t="n">
-        <v>0.91066057700195</v>
+        <v>0.0739907051401821</v>
       </c>
       <c r="G5" t="n">
-        <v>0.970491681144286</v>
+        <v>0.197688380869459</v>
       </c>
     </row>
     <row r="6">
@@ -584,16 +578,16 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.00422677676728277</v>
+        <v>-0.00469261581250222</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.94483114184359</v>
+        <v>-1.05555758593236</v>
       </c>
       <c r="F6" t="n">
-        <v>0.346093940619839</v>
+        <v>0.292950470668537</v>
       </c>
       <c r="G6" t="n">
-        <v>0.589723590915499</v>
+        <v>0.537075862892317</v>
       </c>
     </row>
     <row r="7">
@@ -607,16 +601,16 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.000358406360268043</v>
+        <v>0.0000992702439105307</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0801162467905194</v>
+        <v>0.022329861042096</v>
       </c>
       <c r="F7" t="n">
-        <v>0.936239593660467</v>
+        <v>0.982215957423943</v>
       </c>
       <c r="G7" t="n">
-        <v>0.970491681144286</v>
+        <v>0.982215957423943</v>
       </c>
     </row>
     <row r="8">
@@ -630,16 +624,16 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>0.00408127632500469</v>
+        <v>0.0127342715956098</v>
       </c>
       <c r="E8" t="n">
-        <v>0.912306748769308</v>
+        <v>2.86444864040584</v>
       </c>
       <c r="F8" t="n">
-        <v>0.362906825178769</v>
+        <v>0.00480717863144608</v>
       </c>
       <c r="G8" t="n">
-        <v>0.589723590915499</v>
+        <v>0.0528789649459069</v>
       </c>
     </row>
     <row r="9">
@@ -653,16 +647,16 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0112764971295516</v>
+        <v>-0.00105392080222483</v>
       </c>
       <c r="E9" t="n">
-        <v>2.52068804328163</v>
+        <v>-0.237069076653677</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0126388777647659</v>
+        <v>0.812942485348711</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0622053428530762</v>
+        <v>0.894236733883582</v>
       </c>
     </row>
     <row r="10">
@@ -676,16 +670,16 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0086382199577701</v>
+        <v>-0.00334583470924809</v>
       </c>
       <c r="E10" t="n">
-        <v>1.93094163130901</v>
+        <v>-0.752612476651785</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0551638805784078</v>
+        <v>0.452919951626702</v>
       </c>
       <c r="G10" t="n">
-        <v>0.14342608950386</v>
+        <v>0.622764933486715</v>
       </c>
     </row>
     <row r="11">
@@ -699,16 +693,16 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>0.000265028915287835</v>
+        <v>0.00381847872935854</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0592431506180418</v>
+        <v>0.858929081463959</v>
       </c>
       <c r="F11" t="n">
-        <v>0.952828435672157</v>
+        <v>0.391817150113165</v>
       </c>
       <c r="G11" t="n">
-        <v>0.970491681144286</v>
+        <v>0.615712664463545</v>
       </c>
     </row>
     <row r="12">
@@ -722,62 +716,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>0.010733741898601</v>
+        <v>-0.0112009550692398</v>
       </c>
       <c r="E12" t="n">
-        <v>2.39936343286688</v>
+        <v>-2.51954422979264</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0175113599576275</v>
+        <v>0.0128500715095842</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0622053428530762</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>7</v>
-      </c>
-      <c r="B13" t="n">
-        <v>15</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.00352546164579945</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.788062898923292</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.43176388034538</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.62365893827666</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>7</v>
-      </c>
-      <c r="B14" t="n">
-        <v>15</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>-0.00411803885045364</v>
-      </c>
-      <c r="E14" t="n">
-        <v>-0.920524447694373</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.358610879208931</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.589723590915499</v>
+        <v>0.070675393302713</v>
       </c>
     </row>
   </sheetData>
@@ -816,7 +764,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B2" t="n">
         <v>15</v>
@@ -825,21 +773,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0000116150061375316</v>
+        <v>-0.00000783280817018141</v>
       </c>
       <c r="E2" t="n">
-        <v>0.419365032808131</v>
+        <v>-0.282120635388503</v>
       </c>
       <c r="F2" t="n">
-        <v>0.675481950496014</v>
+        <v>0.778258906247363</v>
       </c>
       <c r="G2" t="n">
-        <v>0.903435656664383</v>
+        <v>0.881801289588927</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B3" t="n">
         <v>15</v>
@@ -848,21 +796,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.0000222131504420585</v>
+        <v>-0.0000257705419677489</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.802015810719622</v>
+        <v>-0.928198612334843</v>
       </c>
       <c r="F3" t="n">
-        <v>0.423670116727492</v>
+        <v>0.354868620536257</v>
       </c>
       <c r="G3" t="n">
-        <v>0.831516968863881</v>
+        <v>0.881801289588927</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B4" t="n">
         <v>15</v>
@@ -871,21 +819,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.000041107575562019</v>
+        <v>-0.0000243206436914464</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.48420754755558</v>
+        <v>-0.875976444490067</v>
       </c>
       <c r="F4" t="n">
-        <v>0.139616577982451</v>
+        <v>0.382511904982897</v>
       </c>
       <c r="G4" t="n">
-        <v>0.762271282899285</v>
+        <v>0.881801289588927</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B5" t="n">
         <v>15</v>
@@ -894,21 +842,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0000333016898970249</v>
+        <v>0.0000162205768505554</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.20237252661495</v>
+        <v>0.584229735750153</v>
       </c>
       <c r="F5" t="n">
-        <v>0.230901179820347</v>
+        <v>0.559986274187242</v>
       </c>
       <c r="G5" t="n">
-        <v>0.762271282899285</v>
+        <v>0.881801289588927</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B6" t="n">
         <v>15</v>
@@ -917,21 +865,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>0.00000831264235804398</v>
+        <v>0.00000630013652651706</v>
       </c>
       <c r="E6" t="n">
-        <v>0.300131699796434</v>
+        <v>0.226917151713438</v>
       </c>
       <c r="F6" t="n">
-        <v>0.764445555639093</v>
+        <v>0.820812234379507</v>
       </c>
       <c r="G6" t="n">
-        <v>0.903435656664383</v>
+        <v>0.881801289588927</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B7" t="n">
         <v>15</v>
@@ -940,21 +888,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0000102270454045205</v>
+        <v>0.0000114454640060496</v>
       </c>
       <c r="E7" t="n">
-        <v>0.369252084830016</v>
+        <v>0.412240604844044</v>
       </c>
       <c r="F7" t="n">
-        <v>0.712402067673943</v>
+        <v>0.680780407525168</v>
       </c>
       <c r="G7" t="n">
-        <v>0.903435656664383</v>
+        <v>0.881801289588927</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B8" t="n">
         <v>15</v>
@@ -963,21 +911,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0000330418576972965</v>
+        <v>0.0000611176068283863</v>
       </c>
       <c r="E8" t="n">
-        <v>1.19299116790765</v>
+        <v>2.20132265430544</v>
       </c>
       <c r="F8" t="n">
-        <v>0.234545010122857</v>
+        <v>0.0293163756802884</v>
       </c>
       <c r="G8" t="n">
-        <v>0.762271282899285</v>
+        <v>0.322480132483172</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B9" t="n">
         <v>15</v>
@@ -986,21 +934,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0000593993075279832</v>
+        <v>0.0000122269789281414</v>
       </c>
       <c r="E9" t="n">
-        <v>2.14463877636372</v>
+        <v>0.440389064706176</v>
       </c>
       <c r="F9" t="n">
-        <v>0.033410434772231</v>
+        <v>0.660320311289257</v>
       </c>
       <c r="G9" t="n">
-        <v>0.434335652039003</v>
+        <v>0.881801289588927</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B10" t="n">
         <v>15</v>
@@ -1009,21 +957,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0000182127596045539</v>
+        <v>-0.0000169887177689834</v>
       </c>
       <c r="E10" t="n">
-        <v>0.657579896097542</v>
+        <v>-0.611896493222884</v>
       </c>
       <c r="F10" t="n">
-        <v>0.511702750070081</v>
+        <v>0.541577891831057</v>
       </c>
       <c r="G10" t="n">
-        <v>0.831516968863881</v>
+        <v>0.881801289588927</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B11" t="n">
         <v>15</v>
@@ -1032,21 +980,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>0.00000434104414436741</v>
+        <v>0.00000413551157795411</v>
       </c>
       <c r="E11" t="n">
-        <v>0.156735355837794</v>
+        <v>0.148952090831289</v>
       </c>
       <c r="F11" t="n">
-        <v>0.875640505483293</v>
+        <v>0.881801289588927</v>
       </c>
       <c r="G11" t="n">
-        <v>0.906919724232953</v>
+        <v>0.881801289588927</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B12" t="n">
         <v>15</v>
@@ -1055,62 +1003,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0000222953042588416</v>
+        <v>-0.0000406604425882328</v>
       </c>
       <c r="E12" t="n">
-        <v>0.804982011310705</v>
+        <v>-1.46450029784201</v>
       </c>
       <c r="F12" t="n">
-        <v>0.421961106427523</v>
+        <v>0.145252287708807</v>
       </c>
       <c r="G12" t="n">
-        <v>0.831516968863881</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>21</v>
-      </c>
-      <c r="B13" t="n">
-        <v>15</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.00000324328223147421</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.117100167085857</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.906919724232953</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.906919724232953</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" t="n">
-        <v>15</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>-0.0000196050136280696</v>
-      </c>
-      <c r="E14" t="n">
-        <v>-0.707847855264803</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.480014810116776</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.831516968863881</v>
+        <v>0.798887582398436</v>
       </c>
     </row>
   </sheetData>
@@ -1149,7 +1051,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B2" t="n">
         <v>15</v>
@@ -1158,21 +1060,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>0.00000901574866273541</v>
+        <v>-0.0000153722582603429</v>
       </c>
       <c r="E2" t="n">
-        <v>0.302432836957191</v>
+        <v>-0.515191692274695</v>
       </c>
       <c r="F2" t="n">
-        <v>0.762694023726838</v>
+        <v>0.607214561286044</v>
       </c>
       <c r="G2" t="n">
-        <v>0.901365664404445</v>
+        <v>0.944225805101644</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B3" t="n">
         <v>15</v>
@@ -1181,21 +1083,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.0000281804905754967</v>
+        <v>-0.000028498440308171</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.945313143745848</v>
+        <v>-0.955107534683619</v>
       </c>
       <c r="F3" t="n">
-        <v>0.345848602544068</v>
+        <v>0.341135119938987</v>
       </c>
       <c r="G3" t="n">
-        <v>0.673519202414681</v>
+        <v>0.833768490458009</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B4" t="n">
         <v>15</v>
@@ -1204,21 +1106,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.0000408731552977193</v>
+        <v>-0.0000271134469603955</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.37108794560502</v>
+        <v>-0.908690342456863</v>
       </c>
       <c r="F4" t="n">
-        <v>0.17216548763728</v>
+        <v>0.365042512313639</v>
       </c>
       <c r="G4" t="n">
-        <v>0.673519202414681</v>
+        <v>0.833768490458009</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B5" t="n">
         <v>15</v>
@@ -1227,21 +1129,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0000359581860323573</v>
+        <v>0.0000220220509735622</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.20621554797211</v>
+        <v>0.738055366770556</v>
       </c>
       <c r="F5" t="n">
-        <v>0.229420283135842</v>
+        <v>0.461690280086803</v>
       </c>
       <c r="G5" t="n">
-        <v>0.673519202414681</v>
+        <v>0.846432180159138</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B6" t="n">
         <v>15</v>
@@ -1250,21 +1152,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.000000346910628812208</v>
+        <v>-0.00000171879435906221</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0116370996538458</v>
+        <v>-0.0576043258915237</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9907288734096</v>
+        <v>0.95414421814559</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9907288734096</v>
+        <v>0.95414421814559</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B7" t="n">
         <v>15</v>
@@ -1273,21 +1175,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0000104020791072156</v>
+        <v>0.00000864080723470735</v>
       </c>
       <c r="E7" t="n">
-        <v>0.348937222224409</v>
+        <v>0.289591290132866</v>
       </c>
       <c r="F7" t="n">
-        <v>0.72757079437128</v>
+        <v>0.772548385992254</v>
       </c>
       <c r="G7" t="n">
-        <v>0.901365664404445</v>
+        <v>0.944225805101644</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B8" t="n">
         <v>15</v>
@@ -1296,21 +1198,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0000279580910134805</v>
+        <v>0.0000630094824936326</v>
       </c>
       <c r="E8" t="n">
-        <v>0.937852761586284</v>
+        <v>2.11172368857425</v>
       </c>
       <c r="F8" t="n">
-        <v>0.349658449756821</v>
+        <v>0.0364490781084556</v>
       </c>
       <c r="G8" t="n">
-        <v>0.673519202414681</v>
+        <v>0.400939859193011</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B9" t="n">
         <v>15</v>
@@ -1319,21 +1221,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>0.000059757250289676</v>
+        <v>0.00000505121969077171</v>
       </c>
       <c r="E9" t="n">
-        <v>2.00455396550333</v>
+        <v>0.169288492065829</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0466074913768936</v>
+        <v>0.865808964593297</v>
       </c>
       <c r="G9" t="n">
-        <v>0.605897387899617</v>
+        <v>0.952389861052627</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B10" t="n">
         <v>15</v>
@@ -1342,21 +1244,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0000233875715081995</v>
+        <v>-0.0000263320853199215</v>
       </c>
       <c r="E10" t="n">
-        <v>0.784534913888995</v>
+        <v>-0.882503492157006</v>
       </c>
       <c r="F10" t="n">
-        <v>0.433824612468255</v>
+        <v>0.378985677480913</v>
       </c>
       <c r="G10" t="n">
-        <v>0.704964995260914</v>
+        <v>0.833768490458009</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B11" t="n">
         <v>15</v>
@@ -1365,21 +1267,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>0.00000483203846544513</v>
+        <v>0.00000997041159347656</v>
       </c>
       <c r="E11" t="n">
-        <v>0.162090488106781</v>
+        <v>0.334152154779362</v>
       </c>
       <c r="F11" t="n">
-        <v>0.871428229415842</v>
+        <v>0.738754294025584</v>
       </c>
       <c r="G11" t="n">
-        <v>0.944047248533829</v>
+        <v>0.944225805101644</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B12" t="n">
         <v>15</v>
@@ -1388,62 +1290,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0000272103327405134</v>
+        <v>-0.0000412679898669697</v>
       </c>
       <c r="E12" t="n">
-        <v>0.912769247802633</v>
+        <v>-1.38307106062534</v>
       </c>
       <c r="F12" t="n">
-        <v>0.362664185915598</v>
+        <v>0.168798763919591</v>
       </c>
       <c r="G12" t="n">
-        <v>0.673519202414681</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>22</v>
-      </c>
-      <c r="B13" t="n">
-        <v>15</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.00000909479474243579</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.305084433738381</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.760677255907894</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.901365664404445</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>22</v>
-      </c>
-      <c r="B14" t="n">
-        <v>15</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>-0.0000293139715130534</v>
-      </c>
-      <c r="E14" t="n">
-        <v>-0.98333570497796</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.326847907319183</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.673519202414681</v>
+        <v>0.833768490458009</v>
       </c>
     </row>
   </sheetData>
@@ -1482,7 +1338,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B2" t="n">
         <v>15</v>
@@ -1491,21 +1347,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.0189282140002292</v>
+        <v>-0.0452883899681252</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.921830478425221</v>
+        <v>-2.21286823942837</v>
       </c>
       <c r="F2" t="n">
-        <v>0.357931111864445</v>
+        <v>0.0284919214813192</v>
       </c>
       <c r="G2" t="n">
-        <v>0.607720472383418</v>
+        <v>0.0981913181783227</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B3" t="n">
         <v>15</v>
@@ -1514,21 +1370,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.0508178387800759</v>
+        <v>0.0498207388970318</v>
       </c>
       <c r="E3" t="n">
-        <v>-2.47489977842632</v>
+        <v>2.43432656466015</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0143138225415893</v>
+        <v>0.0161519909594377</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0620265643468868</v>
+        <v>0.0981913181783227</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B4" t="n">
         <v>15</v>
@@ -1537,21 +1393,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.0318811189937094</v>
+        <v>-0.0442408738243604</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.55265505632738</v>
+        <v>-2.16168480794721</v>
       </c>
       <c r="F4" t="n">
-        <v>0.122376236065699</v>
+        <v>0.0323066634987155</v>
       </c>
       <c r="G4" t="n">
-        <v>0.26514851147568</v>
+        <v>0.0981913181783227</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B5" t="n">
         <v>15</v>
@@ -1560,21 +1416,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>0.052830038687153</v>
+        <v>0.0419550308732113</v>
       </c>
       <c r="E5" t="n">
-        <v>2.57289672642181</v>
+        <v>2.04999460941113</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0109444465428246</v>
+        <v>0.0421919189132246</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0620265643468868</v>
+        <v>0.0981913181783227</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B6" t="n">
         <v>15</v>
@@ -1583,21 +1439,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0401780885559919</v>
+        <v>-0.0414623818293831</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.95672907096953</v>
+        <v>-2.02592293402061</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0520270947291723</v>
+        <v>0.044632417353783</v>
       </c>
       <c r="G6" t="n">
-        <v>0.135270446295848</v>
+        <v>0.0981913181783227</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B7" t="n">
         <v>15</v>
@@ -1606,21 +1462,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.016713237327505</v>
+        <v>-0.0191192063662257</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.813958018514672</v>
+        <v>-0.934197143256247</v>
       </c>
       <c r="F7" t="n">
-        <v>0.416814378375377</v>
+        <v>0.351776996418832</v>
       </c>
       <c r="G7" t="n">
-        <v>0.607720472383418</v>
+        <v>0.463688328482332</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B8" t="n">
         <v>15</v>
@@ -1629,21 +1485,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0050569239399818</v>
+        <v>0.0205766389052755</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.246279264113188</v>
+        <v>1.00540979133322</v>
       </c>
       <c r="F8" t="n">
-        <v>0.805764932786277</v>
+        <v>0.316397810795954</v>
       </c>
       <c r="G8" t="n">
-        <v>0.805764932786277</v>
+        <v>0.463688328482332</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B9" t="n">
         <v>15</v>
@@ -1652,21 +1508,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0129937020541884</v>
+        <v>-0.016497182807289</v>
       </c>
       <c r="E9" t="n">
-        <v>0.632811451782099</v>
+        <v>-0.806080584891345</v>
       </c>
       <c r="F9" t="n">
-        <v>0.527712086994641</v>
+        <v>0.421534844074847</v>
       </c>
       <c r="G9" t="n">
-        <v>0.683263641239524</v>
+        <v>0.463688328482332</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B10" t="n">
         <v>15</v>
@@ -1675,21 +1531,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0457340257858649</v>
+        <v>0.00844550262052957</v>
       </c>
       <c r="E10" t="n">
-        <v>2.22731097978841</v>
+        <v>0.412661711492337</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0272470798147534</v>
+        <v>0.680472516888688</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0885530093979485</v>
+        <v>0.680472516888688</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B11" t="n">
         <v>15</v>
@@ -1698,21 +1554,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.0114406031239734</v>
+        <v>0.0179354469730886</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.557173363060971</v>
+        <v>0.876356633446963</v>
       </c>
       <c r="F11" t="n">
-        <v>0.578146157971905</v>
+        <v>0.382305952698455</v>
       </c>
       <c r="G11" t="n">
-        <v>0.683263641239524</v>
+        <v>0.463688328482332</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B12" t="n">
         <v>15</v>
@@ -1721,62 +1577,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0542808399881449</v>
+        <v>-0.0339578479680035</v>
       </c>
       <c r="E12" t="n">
-        <v>2.64355277761487</v>
+        <v>-1.65923856645423</v>
       </c>
       <c r="F12" t="n">
-        <v>0.00897605676317191</v>
+        <v>0.0992593471100743</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0620265643468868</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>23</v>
-      </c>
-      <c r="B13" t="n">
-        <v>15</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.0165729108854659</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.807123924648286</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.420729557803905</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.607720472383418</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>23</v>
-      </c>
-      <c r="B14" t="n">
-        <v>15</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.00536892931128902</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.26147436179646</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.794045106604698</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.805764932786277</v>
+        <v>0.181975469701803</v>
       </c>
     </row>
   </sheetData>
@@ -1815,7 +1625,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B2" t="n">
         <v>15</v>
@@ -1824,21 +1634,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>0.000221686674985814</v>
+        <v>0.000873939064023384</v>
       </c>
       <c r="E2" t="n">
-        <v>0.177381234333359</v>
+        <v>0.680874581258636</v>
       </c>
       <c r="F2" t="n">
-        <v>0.859468230196996</v>
+        <v>0.497051877157776</v>
       </c>
       <c r="G2" t="n">
-        <v>0.923603746584102</v>
+        <v>0.824822250300696</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B3" t="n">
         <v>15</v>
@@ -1847,21 +1657,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>0.000707332939178</v>
+        <v>0.000674838590842321</v>
       </c>
       <c r="E3" t="n">
-        <v>0.540948209431949</v>
+        <v>0.525757986880238</v>
       </c>
       <c r="F3" t="n">
-        <v>0.589412698606674</v>
+        <v>0.599870727491415</v>
       </c>
       <c r="G3" t="n">
-        <v>0.923603746584102</v>
+        <v>0.824822250300696</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B4" t="n">
         <v>15</v>
@@ -1870,21 +1680,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.000851049429876441</v>
+        <v>0.000301103218594223</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.656370188175393</v>
+        <v>0.234585609358324</v>
       </c>
       <c r="F4" t="n">
-        <v>0.51267555620999</v>
+        <v>0.81486593366262</v>
       </c>
       <c r="G4" t="n">
-        <v>0.923603746584102</v>
+        <v>0.843367705183174</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B5" t="n">
         <v>15</v>
@@ -1893,21 +1703,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>0.000740200256020577</v>
+        <v>-0.00101399368785519</v>
       </c>
       <c r="E5" t="n">
-        <v>0.566177907702213</v>
+        <v>-0.789989320810161</v>
       </c>
       <c r="F5" t="n">
-        <v>0.572189557729852</v>
+        <v>0.430842044694826</v>
       </c>
       <c r="G5" t="n">
-        <v>0.923603746584102</v>
+        <v>0.824822250300696</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B6" t="n">
         <v>15</v>
@@ -1916,21 +1726,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>0.000755742333580241</v>
+        <v>0.000785484170594167</v>
       </c>
       <c r="E6" t="n">
-        <v>0.589221873048931</v>
+        <v>0.611960521911492</v>
       </c>
       <c r="F6" t="n">
-        <v>0.556672805812459</v>
+        <v>0.541535646217197</v>
       </c>
       <c r="G6" t="n">
-        <v>0.923603746584102</v>
+        <v>0.824822250300696</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B7" t="n">
         <v>15</v>
@@ -1939,21 +1749,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.000288032115783406</v>
+        <v>0.000254075498524383</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.225920335560071</v>
+        <v>0.197946923060576</v>
       </c>
       <c r="F7" t="n">
-        <v>0.821596601337146</v>
+        <v>0.843367705183174</v>
       </c>
       <c r="G7" t="n">
-        <v>0.923603746584102</v>
+        <v>0.843367705183174</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B8" t="n">
         <v>15</v>
@@ -1962,21 +1772,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>0.000701323523878374</v>
+        <v>0.000290113123475325</v>
       </c>
       <c r="E8" t="n">
-        <v>0.545921483881638</v>
+        <v>0.226023368900022</v>
       </c>
       <c r="F8" t="n">
-        <v>0.585998607002906</v>
+        <v>0.821505979127692</v>
       </c>
       <c r="G8" t="n">
-        <v>0.923603746584102</v>
+        <v>0.843367705183174</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B9" t="n">
         <v>15</v>
@@ -1985,21 +1795,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>0.000465427958433079</v>
+        <v>0.000948967044052837</v>
       </c>
       <c r="E9" t="n">
-        <v>0.357087230913922</v>
+        <v>0.739327906654179</v>
       </c>
       <c r="F9" t="n">
-        <v>0.72157027866086</v>
+        <v>0.46091980082729</v>
       </c>
       <c r="G9" t="n">
-        <v>0.923603746584102</v>
+        <v>0.824822250300696</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B10" t="n">
         <v>15</v>
@@ -2008,21 +1818,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.000864720329847368</v>
+        <v>0.00127303132161152</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.67849208723397</v>
+        <v>0.991802179022613</v>
       </c>
       <c r="F10" t="n">
-        <v>0.498592412900756</v>
+        <v>0.322969288513135</v>
       </c>
       <c r="G10" t="n">
-        <v>0.923603746584102</v>
+        <v>0.824822250300696</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B11" t="n">
         <v>15</v>
@@ -2031,21 +1841,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>0.000443628888870954</v>
+        <v>-0.00102689218052285</v>
       </c>
       <c r="E11" t="n">
-        <v>0.355987389336784</v>
+        <v>-0.800038369028156</v>
       </c>
       <c r="F11" t="n">
-        <v>0.722391945395287</v>
+        <v>0.425015614003013</v>
       </c>
       <c r="G11" t="n">
-        <v>0.923603746584102</v>
+        <v>0.824822250300696</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B12" t="n">
         <v>15</v>
@@ -2054,62 +1864,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>0.000126083566836552</v>
+        <v>-0.0007014598144798</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0960702151166955</v>
+        <v>-0.546498236679023</v>
       </c>
       <c r="F12" t="n">
-        <v>0.923603746584102</v>
+        <v>0.585575189150279</v>
       </c>
       <c r="G12" t="n">
-        <v>0.923603746584102</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>24</v>
-      </c>
-      <c r="B13" t="n">
-        <v>15</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>-0.00105517900758192</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-0.824500819603965</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.411073467510128</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.923603746584102</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>24</v>
-      </c>
-      <c r="B14" t="n">
-        <v>15</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.0014454411693958</v>
-      </c>
-      <c r="E14" t="n">
-        <v>1.14631101123335</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.253644112531083</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.923603746584102</v>
+        <v>0.824822250300696</v>
       </c>
     </row>
   </sheetData>
@@ -2148,7 +1912,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B2" t="n">
         <v>14</v>
@@ -2157,21 +1921,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>0.00149104818381423</v>
+        <v>-0.000374157819017658</v>
       </c>
       <c r="E2" t="n">
-        <v>0.247887175824078</v>
+        <v>-0.0581987786152955</v>
       </c>
       <c r="F2" t="n">
-        <v>0.804961707359904</v>
+        <v>0.953678304556691</v>
       </c>
       <c r="G2" t="n">
-        <v>0.989374626259194</v>
+        <v>0.953678304556691</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B3" t="n">
         <v>14</v>
@@ -2180,21 +1944,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.00239923652031817</v>
+        <v>-0.00246085068208675</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.364617531104342</v>
+        <v>-0.382775654476718</v>
       </c>
       <c r="F3" t="n">
-        <v>0.716517786915365</v>
+        <v>0.702501784696838</v>
       </c>
       <c r="G3" t="n">
-        <v>0.989374626259194</v>
+        <v>0.953678304556691</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B4" t="n">
         <v>14</v>
@@ -2203,21 +1967,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.0000527775199100832</v>
+        <v>-0.00247832068504423</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.0081124190880319</v>
+        <v>-0.385493044793994</v>
       </c>
       <c r="F4" t="n">
-        <v>0.993550827273856</v>
+        <v>0.700492679545516</v>
       </c>
       <c r="G4" t="n">
-        <v>0.993550827273856</v>
+        <v>0.953678304556691</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B5" t="n">
         <v>14</v>
@@ -2226,21 +1990,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.00271632558037764</v>
+        <v>0.00416801415776077</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.417844058981206</v>
+        <v>0.648318225367591</v>
       </c>
       <c r="F5" t="n">
-        <v>0.677365291726296</v>
+        <v>0.517905348792618</v>
       </c>
       <c r="G5" t="n">
-        <v>0.989374626259194</v>
+        <v>0.953678304556691</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B6" t="n">
         <v>14</v>
@@ -2249,21 +2013,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.000834450507349312</v>
+        <v>-0.00150313104441507</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.131981153056226</v>
+        <v>-0.233806127888408</v>
       </c>
       <c r="F6" t="n">
-        <v>0.895385282491864</v>
+        <v>0.815497713534424</v>
       </c>
       <c r="G6" t="n">
-        <v>0.989374626259194</v>
+        <v>0.953678304556691</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B7" t="n">
         <v>14</v>
@@ -2272,21 +2036,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0026594572157057</v>
+        <v>0.00136919989117898</v>
       </c>
       <c r="E7" t="n">
-        <v>0.430288677131948</v>
+        <v>0.212973663241959</v>
       </c>
       <c r="F7" t="n">
-        <v>0.668333569147435</v>
+        <v>0.831676068153144</v>
       </c>
       <c r="G7" t="n">
-        <v>0.989374626259194</v>
+        <v>0.953678304556691</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B8" t="n">
         <v>14</v>
@@ -2295,21 +2059,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>0.00535722828035734</v>
+        <v>0.00749089132643769</v>
       </c>
       <c r="E8" t="n">
-        <v>0.843521856967801</v>
+        <v>1.16517871277737</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4018664817737</v>
+        <v>0.246047940605263</v>
       </c>
       <c r="G8" t="n">
-        <v>0.989374626259194</v>
+        <v>0.953678304556691</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B9" t="n">
         <v>14</v>
@@ -2318,21 +2082,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>0.00684836577405906</v>
+        <v>0.00291260728628724</v>
       </c>
       <c r="E9" t="n">
-        <v>1.05264744640873</v>
+        <v>0.453044619227717</v>
       </c>
       <c r="F9" t="n">
-        <v>0.296193929178734</v>
+        <v>0.651260423526352</v>
       </c>
       <c r="G9" t="n">
-        <v>0.989374626259194</v>
+        <v>0.953678304556691</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B10" t="n">
         <v>14</v>
@@ -2341,21 +2105,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>0.00396982546651648</v>
+        <v>-0.000695810010933164</v>
       </c>
       <c r="E10" t="n">
-        <v>0.633419533564592</v>
+        <v>-0.108230513238838</v>
       </c>
       <c r="F10" t="n">
-        <v>0.528564520370674</v>
+        <v>0.913977184085161</v>
       </c>
       <c r="G10" t="n">
-        <v>0.989374626259194</v>
+        <v>0.953678304556691</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B11" t="n">
         <v>14</v>
@@ -2364,21 +2128,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.0023614443502669</v>
+        <v>-0.000697164863839837</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.397403317420646</v>
+        <v>-0.108441255285012</v>
       </c>
       <c r="F11" t="n">
-        <v>0.692303099207986</v>
+        <v>0.913810343787454</v>
       </c>
       <c r="G11" t="n">
-        <v>0.989374626259194</v>
+        <v>0.953678304556691</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B12" t="n">
         <v>14</v>
@@ -2387,62 +2151,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>0.00187629640583442</v>
+        <v>-0.00136300717242091</v>
       </c>
       <c r="E12" t="n">
-        <v>0.282775739846254</v>
+        <v>-0.212010410171439</v>
       </c>
       <c r="F12" t="n">
-        <v>0.778199693838765</v>
+        <v>0.832425928723744</v>
       </c>
       <c r="G12" t="n">
-        <v>0.989374626259194</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>25</v>
-      </c>
-      <c r="B13" t="n">
-        <v>14</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>-0.000692362731805005</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-0.109318412351195</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.913268885777718</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.989374626259194</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>25</v>
-      </c>
-      <c r="B14" t="n">
-        <v>14</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>-0.00158483973715082</v>
-      </c>
-      <c r="E14" t="n">
-        <v>-0.25635985991929</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.798439713156035</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.989374626259194</v>
+        <v>0.953678304556691</v>
       </c>
     </row>
   </sheetData>
@@ -2481,7 +2199,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B2" t="n">
         <v>15</v>
@@ -2490,21 +2208,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.023832846061152</v>
+        <v>-0.111266117797261</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.309331431239426</v>
+        <v>-1.44747443860193</v>
       </c>
       <c r="F2" t="n">
-        <v>0.75745046983817</v>
+        <v>0.14995283839449</v>
       </c>
       <c r="G2" t="n">
-        <v>0.883562064629516</v>
+        <v>0.329896244467879</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B3" t="n">
         <v>15</v>
@@ -2513,21 +2231,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.143913513743253</v>
+        <v>0.00224570126247779</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.86788321741643</v>
+        <v>0.029214600441939</v>
       </c>
       <c r="F3" t="n">
-        <v>0.063509640263224</v>
+        <v>0.976734169682802</v>
       </c>
       <c r="G3" t="n">
-        <v>0.288147353867706</v>
+        <v>0.976734169682802</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B4" t="n">
         <v>15</v>
@@ -2536,21 +2254,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.117485886835144</v>
+        <v>-0.122481751563092</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.52487358966274</v>
+        <v>-1.59337998029021</v>
       </c>
       <c r="F4" t="n">
-        <v>0.129159814872912</v>
+        <v>0.113282950741221</v>
       </c>
       <c r="G4" t="n">
-        <v>0.335815518669572</v>
+        <v>0.311528114538357</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B5" t="n">
         <v>15</v>
@@ -2559,21 +2277,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0179962785961489</v>
+        <v>0.126466215290078</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.233577416681435</v>
+        <v>1.64521435278856</v>
       </c>
       <c r="F5" t="n">
-        <v>0.815595751965707</v>
+        <v>0.102121984600397</v>
       </c>
       <c r="G5" t="n">
-        <v>0.883562064629516</v>
+        <v>0.311528114538357</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B6" t="n">
         <v>15</v>
@@ -2582,21 +2300,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0751823630755602</v>
+        <v>-0.0807219342523098</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.975807417815421</v>
+        <v>-1.05012144557452</v>
       </c>
       <c r="F6" t="n">
-        <v>0.330554609746542</v>
+        <v>0.295433726613865</v>
       </c>
       <c r="G6" t="n">
-        <v>0.70279854140913</v>
+        <v>0.541628498792086</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B7" t="n">
         <v>15</v>
@@ -2605,21 +2323,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>0.018948002567245</v>
+        <v>-0.0257794514785002</v>
       </c>
       <c r="E7" t="n">
-        <v>0.245930038662403</v>
+        <v>-0.335368014945036</v>
       </c>
       <c r="F7" t="n">
-        <v>0.806034816069086</v>
+        <v>0.737838981539042</v>
       </c>
       <c r="G7" t="n">
-        <v>0.883562064629516</v>
+        <v>0.892010754712302</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B8" t="n">
         <v>15</v>
@@ -2628,21 +2346,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0489867735269604</v>
+        <v>0.15988709989516</v>
       </c>
       <c r="E8" t="n">
-        <v>0.635809450873607</v>
+        <v>2.07999069925431</v>
       </c>
       <c r="F8" t="n">
-        <v>0.525760682254315</v>
+        <v>0.0393112354955333</v>
       </c>
       <c r="G8" t="n">
-        <v>0.759432096589566</v>
+        <v>0.311528114538357</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B9" t="n">
         <v>15</v>
@@ -2651,21 +2369,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>0.131932603572274</v>
+        <v>-0.0184242624529707</v>
       </c>
       <c r="E9" t="n">
-        <v>1.71238050988287</v>
+        <v>-0.239683467696443</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0886607242669864</v>
+        <v>0.810918867920274</v>
       </c>
       <c r="G9" t="n">
-        <v>0.288147353867706</v>
+        <v>0.892010754712302</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B10" t="n">
         <v>15</v>
@@ -2674,21 +2392,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>0.135061581855299</v>
+        <v>-0.055794472174305</v>
       </c>
       <c r="E10" t="n">
-        <v>1.75299216524798</v>
+        <v>-0.725837064206275</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0814165867945163</v>
+        <v>0.469124924705974</v>
       </c>
       <c r="G10" t="n">
-        <v>0.288147353867706</v>
+        <v>0.645046771470715</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B11" t="n">
         <v>15</v>
@@ -2697,21 +2415,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.00185532091715041</v>
+        <v>0.0572395935638248</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.0240805933642169</v>
+        <v>0.744636823858339</v>
       </c>
       <c r="F11" t="n">
-        <v>0.98081673251839</v>
+        <v>0.457713281145227</v>
       </c>
       <c r="G11" t="n">
-        <v>0.98081673251839</v>
+        <v>0.645046771470715</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B12" t="n">
         <v>15</v>
@@ -2720,62 +2438,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>0.154584769878224</v>
+        <v>-0.125692398807782</v>
       </c>
       <c r="E12" t="n">
-        <v>2.00638765473303</v>
+        <v>-1.63514768019797</v>
       </c>
       <c r="F12" t="n">
-        <v>0.046409612660569</v>
+        <v>0.104217454472809</v>
       </c>
       <c r="G12" t="n">
-        <v>0.288147353867706</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>26</v>
-      </c>
-      <c r="B13" t="n">
-        <v>15</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.0532538171281962</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.691192291049074</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.490393053246413</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.759432096589566</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>26</v>
-      </c>
-      <c r="B14" t="n">
-        <v>15</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>-0.0680405600197775</v>
-      </c>
-      <c r="E14" t="n">
-        <v>-0.883112480953626</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.378429983835685</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.70279854140913</v>
+        <v>0.311528114538357</v>
       </c>
     </row>
   </sheetData>
@@ -2791,71 +2463,71 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" t="s">
         <v>27</v>
-      </c>
-      <c r="B1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C1" t="s">
-        <v>29</v>
       </c>
       <c r="D1" t="s">
         <v>0</v>
       </c>
       <c r="E1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1" t="s">
         <v>30</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>31</v>
-      </c>
-      <c r="G1" t="s">
-        <v>32</v>
-      </c>
-      <c r="H1" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" t="s">
         <v>34</v>
-      </c>
-      <c r="B2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C2" t="s">
-        <v>36</v>
       </c>
       <c r="D2" t="s">
         <v>7</v>
       </c>
       <c r="E2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.00411803885045364</v>
+        <v>0.00469261581250222</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" t="s">
         <v>34</v>
       </c>
-      <c r="B3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C3" t="s">
-        <v>36</v>
-      </c>
       <c r="D3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -2864,24 +2536,24 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0023614443502669</v>
+        <v>0.00150313104441507</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" t="s">
         <v>34</v>
       </c>
-      <c r="B4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C4" t="s">
-        <v>36</v>
-      </c>
       <c r="D4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -2890,24 +2562,24 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0.000707332939178</v>
+        <v>0.000785484170594167</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" t="s">
         <v>34</v>
       </c>
-      <c r="B5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C5" t="s">
-        <v>36</v>
-      </c>
       <c r="D5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F5" t="n">
         <v>1</v>
@@ -2916,24 +2588,24 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0000196050136280696</v>
+        <v>0.0000162205768505554</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" t="s">
         <v>34</v>
       </c>
-      <c r="B6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C6" t="s">
-        <v>36</v>
-      </c>
       <c r="D6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
@@ -2942,50 +2614,50 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0000272103327405134</v>
+        <v>0.0000220220509735622</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" t="s">
         <v>34</v>
       </c>
-      <c r="B7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C7" t="s">
-        <v>36</v>
-      </c>
       <c r="D7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0189282140002292</v>
+        <v>0.0339578479680035</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" t="s">
         <v>34</v>
       </c>
-      <c r="B8" t="s">
-        <v>35</v>
-      </c>
-      <c r="C8" t="s">
-        <v>36</v>
-      </c>
       <c r="D8" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E8" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F8" t="n">
         <v>1</v>
@@ -2994,7 +2666,7 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0680405600197775</v>
+        <v>0.0807219342523098</v>
       </c>
     </row>
   </sheetData>
